--- a/output/Dupuy_Malesia_Candidati_Raggruppati.xlsx
+++ b/output/Dupuy_Malesia_Candidati_Raggruppati.xlsx
@@ -24,7 +24,7 @@
     <sheet name="Sede n.d." sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tutti i risultati'!$A$1:$J$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tutti i risultati'!$A$1:$K$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -563,16 +563,16 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
         <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -619,7 +619,7 @@
         <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -679,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -688,6 +688,9 @@
           <t>Perak</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
@@ -698,7 +701,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -761,7 +764,7 @@
         <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -777,7 +780,7 @@
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
@@ -789,13 +792,13 @@
         <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -899,18 +902,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -951,10 +955,15 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -963,30 +972,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Cleaning</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wah Seng Sin Kee Co Sdn Bhd (WSSK)</t>
+          <t>Floormac (M) Sdn Bhd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ipoh (filiali KL, Kuantan, Butterworth)</t>
+          <t>Ipoh (citta dedotta, non confermata)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Conflitto di marchio</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Distributore di ferramenta dagli anni cinquanta.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>Distributore autorizzato Nilfisk, RCM, FASA, 3M: conflitto di marchio probabile nel Cleaning. 2° giro.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -995,35 +1009,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JESS Technology</t>
+          <t>Wah Seng Sin Kee Co Sdn Bhd (WSSK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ipoh</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://www.jesstechnology.com</t>
+          <t>Ipoh (filiali KL, Kuantan, Butterworth)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Riparazione saldatrici; vendita non confermata.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>Distributore di ferramenta dagli anni cinquanta. | VERIFICA: TBK 365 Jalan Menglembu, Ipoh. Sito NON verificato (wssk.com.my era solo un'ipotesi dell'agente: non usare). Jobstore lo classifica come manifattura, ruolo da chiarire.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1032,30 +1046,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Welding</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JESS Technology</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ipoh</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.jesstechnology.com</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Debole / da verificare</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Riparazione saldatrici; vendita non confermata.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>DA VERIFICARE UMANAMENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Meccanica</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Wah Seng Sin Kee Co Sdn Bhd (WSSK)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Ipoh (filiali KL, Kuantan, Butterworth)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Candidato</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Distributore di ferramenta dagli anni cinquanta.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Parziale</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Distributore di ferramenta dagli anni cinquanta. | VERIFICA: TBK 365 Jalan Menglembu, Ipoh. Sito NON verificato (wssk.com.my era solo un'ipotesi dell'agente: non usare). Jobstore lo classifica come manifattura, ruolo da chiarire.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1072,18 +1133,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1124,10 +1186,15 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -1156,10 +1223,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Forniture elettriche, non confermato.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1188,10 +1260,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Probabile retail al dettaglio.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1208,18 +1285,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1260,10 +1338,15 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -1297,10 +1380,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Utensili elettrici e batterie (Milwaukee). Probabile rivenditore.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>Utensili elettrici e batterie (Milwaukee). Probabile rivenditore. | VERIFICA: Lorong Mutiara Inanam, Kota Kinabalu. Vende Milwaukee: possibile conflitto. Solo profilo marketplace, attivita attuale non provata.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1329,10 +1417,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Riparazioni e zincatura: officina/cliente finale.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1361,10 +1454,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Vetroresina, resine, pigmenti; fit debole.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1398,10 +1496,15 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Ferramenta e vernici; fit con Dupuy debole.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1430,10 +1533,15 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Riparazioni e zincatura: officina/cliente finale.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1450,18 +1558,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1502,10 +1611,15 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -1534,10 +1648,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Materiali edili ed elettroutensili (Makita, HiKOKI).</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>Materiali edili ed elettroutensili (Makita, HiKOKI). | VERIFICA: 248 Teck Guan Building, Jalan Padungan, Kuching. Nessuna fonte su marchi o attivita corrente.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1566,10 +1685,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Grossista macchinari e attrezzature industriali dal 1990.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>Grossista macchinari e attrezzature industriali dal 1990. | VERIFICA: Dati 2024 indicano attivita recente. Marchi e settore non verificati.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1603,10 +1727,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Probabile officina di saldatura.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1630,20 +1759,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pansar.com.my</t>
+          <t>https://pansar.com.my/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Conflitto di marchio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Distributore Lincoln Electric per East Malaysia. Verificare eventuale conflitto di marca.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>Distributore Lincoln Electric per East Malaysia. Verificare eventuale conflitto di marca. | VERIFICA: 23 Jalan Bengkel, Sibu. Dal 1961. DISTRIBUTORE ESCLUSIVO Lincoln Electric da 30+ anni (marchi Arcweld, Duraweld, Optimarc...): conflitto probabile nel Welding. Pagina contatti non aperta.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1672,10 +1806,15 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Ricambi macchine movimento terra; probabilmente fuori target.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1699,20 +1838,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pansar.com.my</t>
+          <t>https://pansar.com.my/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Conflitto di marchio</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Distributore Lincoln Electric per East Malaysia. Verificare eventuale conflitto di marca.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>Distributore Lincoln Electric per East Malaysia. Verificare eventuale conflitto di marca. | VERIFICA: 23 Jalan Bengkel, Sibu. Dal 1961. DISTRIBUTORE ESCLUSIVO Lincoln Electric da 30+ anni (marchi Arcweld, Duraweld, Optimarc...): conflitto probabile nel Welding. Pagina contatti non aperta.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1741,10 +1885,15 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Grossista macchinari e attrezzature industriali dal 1990.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>Grossista macchinari e attrezzature industriali dal 1990. | VERIFICA: Dati 2024 indicano attivita recente. Marchi e settore non verificati.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1761,18 +1910,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1813,10 +1963,15 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -1838,6 +1993,16 @@
           <t>Puchong</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.duromac.com (dal risultato di ricerca, non aperto)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>+60 3 8070 2826 (da risultato di ricerca, non verificato sul sito)</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -1845,10 +2010,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Spazzatrici; rappresenta DISAB-TELLA (aspiratori industriali).</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>Spazzatrici; rappresenta DISAB-TELLA (aspiratori industriali). | VERIFICA: No.9 Jalan BK 1/15, Bandar Kinrara, Puchong. Dal 1996. Rivende spazzatrici di marchi terzi; nulla su depolverazione/aspirazione.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1877,10 +2047,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Tipo di prodotto non chiaro.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1909,10 +2084,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Filiale di produttore.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1939,6 +2119,16 @@
           <t>https://techno.my</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+603-4270 2333</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sales@techno.com.my</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -1946,10 +2136,15 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fornitore autorizzato Kärcher; potrebbe essere più un retailer.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>Fornitore autorizzato Kärcher; potrebbe essere più un retailer. | VERIFICA: 36-1 Jalan Sulaiman 1, Taman Putra Sulaiman, Ampang. Distributore dal 2007, 50+ marchi. CONFLITTI: Karcher (cleaning), DeWalt, Bosch, Makita, Stanley. Generalista MRO.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -1983,10 +2178,15 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Parts cleaning e ultrasuoni.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2015,10 +2215,15 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Edilizia ed elettroutensili, forse poco industriale.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2047,10 +2252,15 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>Probabile entità indonesiana; legame con Malesia incerto.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2077,6 +2287,16 @@
           <t>https://cthardware.com</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>(603) 7873 0000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hello@cthardware.com</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -2084,10 +2304,15 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Distributore ventilatori, soffianti, saldatrici.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
+        <is>
+          <t>Distributore ventilatori, soffianti, saldatrici. | VERIFICA: No.1 Jalan SS2/3, Petaling Jaya. Dal 1977, punti vendita Klang Valley. CONFLITTI: Karcher, Bosch, DeWalt, Makita, Graco; marchi propri Kawa, Welflo, Accubit. Profilo anche DIY/retail.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2111,15 +2336,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Ferramenta e utensili.</t>
+          <t>Non verificabile</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
+        <is>
+          <t>Ferramenta e utensili. | VERIFICA: Solo directory a bassa affidabilita; negozio ferramenta/DIY, 2 Jalan SS 2/63, PJ.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2148,10 +2378,15 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Abrasivi, utensili, gas, saldatura, compressori.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
+        <is>
+          <t>Abrasivi, utensili, gas, saldatura, compressori. | VERIFICA: Klang. Saldatura, abrasivi, utensili, compressori, idropulitrici, gas. Dominio/contatti non verificati. Forse collegata a HLH Industrial Supply (M) Sdn Bhd (non provato).</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2178,6 +2413,16 @@
           <t>https://techno.my</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>+603-4270 2333</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>sales@techno.com.my</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -2185,10 +2430,15 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fornitore autorizzato Kärcher; potrebbe essere più un retailer.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>Fornitore autorizzato Kärcher; potrebbe essere più un retailer. | VERIFICA: 36-1 Jalan Sulaiman 1, Taman Putra Sulaiman, Ampang. Distributore dal 2007, 50+ marchi. CONFLITTI: Karcher (cleaning), DeWalt, Bosch, Makita, Stanley. Generalista MRO.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2210,6 +2460,11 @@
           <t>Seksyen 51A, Petaling Jaya</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://tomac.com.my (compare nei risultati; /about 404, non aperto)</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -2217,10 +2472,15 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fornitore industriale dal 1984.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
+        <is>
+          <t>Fornitore industriale dal 1984. | VERIFICA: Lot 22 Jalan 51A/223, PJ 46100. Dal 1984. Utensili manuali, torque, sollevamento, pneumatici, MRO oil&amp;gas. Marchi non verificati.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2254,10 +2514,15 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>Multinazionale del vuoto, non idonea come distributore.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2291,10 +2556,15 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>Produttore di dust collector e ventilatori.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2316,6 +2586,16 @@
           <t>Puchong</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.duromac.com (dal risultato di ricerca, non aperto)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>+60 3 8070 2826 (da risultato di ricerca, non verificato sul sito)</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -2323,10 +2603,15 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Spazzatrici; rappresenta DISAB-TELLA (aspiratori industriali).</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
+        <is>
+          <t>Spazzatrici; rappresenta DISAB-TELLA (aspiratori industriali). | VERIFICA: No.9 Jalan BK 1/15, Bandar Kinrara, Puchong. Dal 1996. Rivende spazzatrici di marchi terzi; nulla su depolverazione/aspirazione.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2340,12 +2625,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Singuan Blasting Sdn Bhd</t>
+          <t>Master Jaya Environment Sdn Bhd</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
+          <t>Taming Jaya Industrial Park, Seri Kembangan</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>+60389626233</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2355,10 +2645,15 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Costruisce sabbiatrici e depolveratori.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
+        <is>
+          <t>Controllo inquinamento aria, ventilazione, fume cleaning: contractor/produttore, priorita bassa. 2° giro.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2367,30 +2662,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ATEX</t>
+          <t>Depolverazione</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ampmech Sdn Bhd</t>
+          <t>Singuan Blasting Sdn Bhd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Damansara Jaya, Petaling Jaya</t>
+          <t>Shah Alam</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Channel partner Ceag, Rittal, Mennekes; uffici anche a Penang, Bintulu, Miri.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
+        <is>
+          <t>Costruisce sabbiatrici e depolveratori.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2404,30 +2704,45 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Beckhoff Automation Sdn Bhd</t>
+          <t>Ampmech Sdn Bhd</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kota Damansara</t>
+          <t>Damansara Jaya, Petaling Jaya</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://beckhoff.com</t>
+          <t>https://www.ampmech.com</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>+603-7728 6250 / +6016-718 6250</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>info@ampmech.com</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Produttore di automazione: da escludere.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
+        <is>
+          <t>Channel partner Ceag, Rittal, Mennekes; uffici anche a Penang, Bintulu, Miri. | VERIFICA: 46 Jalan SS22/21, Damansara Jaya. Stocking distributor prodotti Ex; ISO 9001; sedi anche a Kemaman, Bintulu, Miri, Penang. Marchi: Eaton Crouse-Hinds, CEAG, Thuba, Mennekes, Gewiss, Rittal, Fluke.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2441,25 +2756,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>See Kwong Electric (KL) Sdn Bhd</t>
+          <t>Beckhoff Automation Sdn Bhd</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Puchong (Jalan TPP 5/2)</t>
+          <t>Kota Damansara</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://beckhoff.com</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Prodotti antideflagranti ATEX/IECEx, attiva dal 1982.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
+        <is>
+          <t>Produttore di automazione: da escludere.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2468,17 +2793,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sabbiatura</t>
+          <t>ATEX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Medias Industrial Supplies Sdn Bhd</t>
+          <t>See Kwong Electric (KL) Sdn Bhd</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
+          <t>Puchong (Jalan TPP 5/2)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2488,10 +2813,15 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Dal 1986: abrasivi, cabine, granigliatrici, ricambi.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
+        <is>
+          <t>Prodotti antideflagranti ATEX/IECEx, attiva dal 1982. | VERIFICA: 14 &amp; 16 Jalan TPP 5/2, Puchong. SSM 87458-A, dal 1982. Stockist ATEX/IECEx. Dominio/contatti non confermati.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2505,25 +2835,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Schmidt Abrasive Blasting</t>
+          <t>Medias Industrial Supplies Sdn Bhd</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Petaling Jaya</t>
+          <t>Shah Alam</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Conflitto di marchio</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Distributore marchio Schmidt, dal 2012: probabile conflitto di marca.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
+        <is>
+          <t>Dal 1986: abrasivi, cabine, granigliatrici, ricambi. | VERIFICA: Shah Alam. Fonte principale: scheda directory indonesiana (identita/indirizzo da riverificare). Ruolo distributore/produttore non chiaro.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2537,25 +2872,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Singuan Blasting Sdn Bhd</t>
+          <t>Schmidt Abrasive Blasting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
+          <t>Petaling Jaya</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Conflitto di marchio</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Costruisce sabbiatrici e depolveratori.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
+        <is>
+          <t>Distributore marchio Schmidt, dal 2012: probabile conflitto di marca.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2564,30 +2904,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Sabbiatura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C-MART &amp; BUDDY TOOLS</t>
+          <t>Singuan Blasting Sdn Bhd</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Non chiara</t>
+          <t>Shah Alam</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Probabile entità indonesiana; legame con Malesia incerto.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
+        <is>
+          <t>Costruisce sabbiatrici e depolveratori.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2601,30 +2946,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CT Hardware</t>
+          <t>C-MART &amp; BUDDY TOOLS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Petaling Jaya</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://cthardware.com</t>
+          <t>Non chiara</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Distributore ventilatori, soffianti, saldatrici.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
+        <is>
+          <t>Probabile entità indonesiana; legame con Malesia incerto.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2638,12 +2983,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HLH Welding Supply</t>
+          <t>CT Hardware</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Klang</t>
+          <t>Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://cthardware.com</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>(603) 7873 0000</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>hello@cthardware.com</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2653,10 +3013,15 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Abrasivi, utensili, gas, saldatura, compressori.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
+        <is>
+          <t>Distributore ventilatori, soffianti, saldatrici. | VERIFICA: No.1 Jalan SS2/3, Petaling Jaya. Dal 1977, punti vendita Klang Valley. CONFLITTI: Karcher, Bosch, DeWalt, Makita, Graco; marchi propri Kawa, Welflo, Accubit. Profilo anche DIY/retail.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2670,12 +3035,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MECHKINARC (M) Sdn Bhd</t>
+          <t>HLH Welding Supply</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
+          <t>Klang</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2685,10 +3050,15 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Macchine taglio e saldatura marchio MORROW.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
+        <is>
+          <t>Abrasivi, utensili, gas, saldatura, compressori. | VERIFICA: Klang. Saldatura, abrasivi, utensili, compressori, idropulitrici, gas. Dominio/contatti non verificati. Forse collegata a HLH Industrial Supply (M) Sdn Bhd (non provato).</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2702,30 +3072,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Techno Tools &amp; Equipment</t>
+          <t>MECHKINARC (M) Sdn Bhd</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ampang</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://techno.my</t>
+          <t>Shah Alam</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Conflitto di marchio</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fornitore autorizzato Kärcher; potrebbe essere più un retailer.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
+        <is>
+          <t>Macchine taglio e saldatura marchio MORROW. | VERIFICA: No.7 Jalan Dermawan 25/89, Shah Alam. Agente esclusivo marchio MORROW (taglio/saldatura): conflitto di marca nel Welding.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2739,25 +3109,45 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TSIS Welding Solution Sdn Bhd</t>
+          <t>Techno Tools &amp; Equipment</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Selangor (città n.d.)</t>
+          <t>Ampang</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://techno.my</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>+603-4270 2333</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>sales@techno.com.my</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Conflitto di marchio</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Distributore esclusivo Fronius dal 2015.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
+        <is>
+          <t>Fornitore autorizzato Kärcher; potrebbe essere più un retailer. | VERIFICA: 36-1 Jalan Sulaiman 1, Taman Putra Sulaiman, Ampang. Distributore dal 2007, 50+ marchi. CONFLITTI: Karcher (cleaning), DeWalt, Bosch, Makita, Stanley. Generalista MRO.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2771,25 +3161,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TSM Welding Technology Sdn Bhd</t>
+          <t>TSIS Welding Solution Sdn Bhd</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Klang</t>
+          <t>Selangor (città n.d.)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Conflitto di marchio</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Saldatura a resistenza: nicchia.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
+        <is>
+          <t>Distributore esclusivo Fronius dal 2015.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2803,25 +3198,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Weld Systems Sdn Bhd</t>
+          <t>TSM Welding Technology Sdn Bhd</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Petaling Jaya</t>
+          <t>Klang</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Vendita, noleggio e riparazione saldatrici e plasma.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
+        <is>
+          <t>Saldatura a resistenza: nicchia.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2830,12 +3230,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CT Hardware</t>
+          <t>Weld Systems Sdn Bhd</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2843,11 +3243,6 @@
           <t>Petaling Jaya</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://cthardware.com</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -2855,10 +3250,15 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Distributore ventilatori, soffianti, saldatrici.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
+        <is>
+          <t>Vendita, noleggio e riparazione saldatrici e plasma. | VERIFICA: 45 Jalan PJU 1A/18, Taman Perindustrian Jaya, PJ. Vende, noleggia, ripara saldatrici. Sito/contatti non verificati.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2872,30 +3272,45 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DAV Engineering Sdn Bhd</t>
+          <t>CT Hardware</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
+          <t>Petaling Jaya</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.exporthub.com/dav-engineering-sdn-bhd/</t>
+          <t>https://cthardware.com</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>(603) 7873 0000</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>hello@cthardware.com</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Produttore di dust collector e ventilatori.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
+        <is>
+          <t>Distributore ventilatori, soffianti, saldatrici. | VERIFICA: No.1 Jalan SS2/3, Petaling Jaya. Dal 1977, punti vendita Klang Valley. CONFLITTI: Karcher, Bosch, DeWalt, Makita, Graco; marchi propri Kawa, Welflo, Accubit. Profilo anche DIY/retail.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2909,7 +3324,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Elta Fans Malaysia Sdn Bhd</t>
+          <t>DAV Engineering Sdn Bhd</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2917,17 +3332,27 @@
           <t>Shah Alam</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.exporthub.com/dav-engineering-sdn-bhd/</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Vendita e distribuzione ventilatori.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
+        <is>
+          <t>Produttore di dust collector e ventilatori.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2941,22 +3366,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Systemair Malaysia</t>
+          <t>Elta Fans Malaysia Sdn Bhd</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kampung Jaya, Selangor 47000</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://www.systemair.my</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>603-6157 1177</t>
+          <t>Shah Alam</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2966,10 +3381,15 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Probabile costruttore/filiale (ventilazione).</t>
+          <t>Scartato</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
+        <is>
+          <t>Vendita e distribuzione ventilatori. | VERIFICA: SCARTATO dopo verifica: produttore (filiale gruppo Elta), non distributore.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -2983,25 +3403,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tools &amp; Machinery Parts Supplies Sdn Bhd (TMP)</t>
+          <t>Luchtech Engineering Sdn Bhd</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seksyen 51A, Petaling Jaya</t>
+          <t>Jalan Utama 2/18, Puchong</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fornitore industriale dal 1984.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
+        <is>
+          <t>Aria compressa (compressori, essiccatori, filtri): settore marginale, solo come partner adiacente. 2° giro.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3015,25 +3440,119 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>Systemair Malaysia</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Kampung Jaya, Selangor 47000</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.systemair.my</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>603-6157 1177</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Produttore / possibile concorrente</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Probabile costruttore/filiale (ventilazione).</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>DA VERIFICARE UMANAMENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Meccanica</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tools &amp; Machinery Parts Supplies Sdn Bhd (TMP)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Seksyen 51A, Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://tomac.com.my (compare nei risultati; /about 404, non aperto)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Candidato</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Parziale</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Fornitore industriale dal 1984. | VERIFICA: Lot 22 Jalan 51A/223, PJ 46100. Dal 1984. Utensili manuali, torque, sollevamento, pneumatici, MRO oil&amp;gas. Marchi non verificati.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>DA VERIFICARE UMANAMENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Meccanica</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>Vostermans Ventilation Sdn Bhd</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Klang</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Produttore / possibile concorrente</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>Probabile costruttore.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3050,18 +3569,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3102,10 +3622,15 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -3139,10 +3664,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Aggregatore con 10.000+ fornitori, non distributore diretto. Compare nei risultati di quasi tutti gli stati.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3176,10 +3706,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Rappresenta Tennant: probabile conflitto di marca.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3213,10 +3748,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Filiale di produttore.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3245,10 +3785,15 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Dichiara 50 anni di attività; sede non chiara.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3282,10 +3827,15 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Aggregatore con 10.000+ fornitori, non distributore diretto. Compare nei risultati di quasi tutti gli stati.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3319,10 +3869,15 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Compare per Kota Kinabalu e Sarawak; sede non confermata.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3356,10 +3911,15 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>Illuminazione antideflagrante, distributore dal 2004.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3388,10 +3948,15 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Sede non determinata.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3425,10 +3990,15 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Aggregatore con 10.000+ fornitori, non distributore diretto. Compare nei risultati di quasi tutti gli stati.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3457,10 +4027,15 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Stockist dal 1993; filiale in Kedah non confermata.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3489,10 +4064,15 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>Dichiara 50 anni di attività; sede non chiara.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3526,10 +4106,15 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>Aggregatore con 10.000+ fornitori, non distributore diretto. Compare nei risultati di quasi tutti gli stati.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3563,10 +4148,15 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>Compare per Kota Kinabalu e Sarawak; sede non confermata.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3583,7 +4173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3591,11 +4181,12 @@
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3641,10 +4232,15 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -3681,10 +4277,15 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
           <t>Detergenti e chimici, non attrezzature: probabilmente fuori target.</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3725,10 +4326,15 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>Chimici per pulizia industriale. Fonte debole, probabilmente fuori target.</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3765,10 +4371,15 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Elettroutensili, saldatrici, DPI. Fonte poco affidabile.</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3795,7 +4406,11 @@
           <t>Muar</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>http://www.glbosun.com.my/</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="inlineStr">
@@ -3805,10 +4420,15 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Utensili e ferramenta, fondata 2000.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Utensili e ferramenta, fondata 2000. | VERIFICA: Lot 1745 Jalan Naib Kadir, Bukit Pasir, Muar. Sito citato nei risultati, non aperto. Nome Bosun = marchio cinese: possibile conflitto su utensili diamantati/elettrici.</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3835,7 +4455,11 @@
           <t>Johor Bahru</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>http://www.sumitec.my</t>
+        </is>
+      </c>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="inlineStr">
@@ -3845,10 +4469,15 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Utensili di precisione, misura, manutenzione. Fondata 2007.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Utensili di precisione, misura, manutenzione. Fondata 2007. | VERIFICA: No.35 Jalan Tiong Emas, Tiong Nam, Johor Bahru. Distributore di utensili di precisione/misura da principals. Sito citato, non aperto.</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3889,10 +4518,15 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Attrezzature sabbiatura, rivestimenti, DPI. Fondata 1997. Sito proprio non trovato (pagina directory).</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Attrezzature sabbiatura, rivestimenti, DPI. Fondata 1997. Sito proprio non trovato (pagina directory). | VERIFICA: Sede discordante (Singapore o Johor Bahru); un'unica fonte; sito non trovato.</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3929,10 +4563,15 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
           <t>Elettroutensili, saldatrici, DPI. Fonte poco affidabile.</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -3969,10 +4608,15 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
           <t>Produttore di saldatrici automatiche e fili animati.</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4009,10 +4653,15 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Rivenditore dal 1991: utensili, saldatura, aspirapolveri, compressori. Candidato più rilevante in Kedah.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Rivenditore dal 1991: utensili, saldatura, aspirapolveri, compressori. Candidato più rilevante in Kedah. | VERIFICA: Vende/ripara/noleggia macchinari (pompe, compressori, soffiatori, lavapavimenti, aspirapolvere). Coerente con Cleaning, meno con Utensileria e Welding.</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4053,10 +4702,15 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
           <t>Il nome indica un produttore.</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4075,15 +4729,19 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>H.E. Trading (S.P) Sdn. Bhd.</t>
+          <t>CR Hardware Sdn Bhd</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Sungai Petani (Jalan Kuala Ketil)</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n"/>
+          <t>250-C Jalan Tunku Putra, Kulim</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>https://mall.lapasar.com/supplier-profile/cr-hardware</t>
+        </is>
+      </c>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="3" t="inlineStr">
@@ -4093,10 +4751,15 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Rivenditore dal 1991: utensili, saldatura, aspirapolveri, compressori. Candidato più rilevante in Kedah.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Utensili manuali ed elettrici, fornitore B2B (profilo marketplace). 2° giro.</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4110,7 +4773,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -4133,10 +4796,15 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Rivenditore dal 1991: utensili, saldatura, aspirapolveri, compressori. Candidato più rilevante in Kedah.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Rivenditore dal 1991: utensili, saldatura, aspirapolveri, compressori. Candidato più rilevante in Kedah. | VERIFICA: Vende/ripara/noleggia macchinari (pompe, compressori, soffiatori, lavapavimenti, aspirapolvere). Coerente con Cleaning, meno con Utensileria e Welding.</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4145,22 +4813,22 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Kelantan</t>
+          <t>Kedah</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>G&amp;T Hyper Hardware</t>
+          <t>H.E. Trading (S.P) Sdn. Bhd.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Sede citata a Sungai Pelong (stato non confermato)</t>
+          <t>Sungai Petani (Jalan Kuala Ketil)</t>
         </is>
       </c>
       <c r="E14" s="3" t="n"/>
@@ -4168,15 +4836,20 @@
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Catena ferramenta; presenza in Kelantan non confermata.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Rivenditore dal 1991: utensili, saldatura, aspirapolveri, compressori. Candidato più rilevante in Kedah. | VERIFICA: Vende/ripara/noleggia macchinari (pompe, compressori, soffiatori, lavapavimenti, aspirapolvere). Coerente con Cleaning, meno con Utensileria e Welding.</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4190,25 +4863,21 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>SLS Kelantan Sdn. Bhd.</t>
+          <t>G&amp;T Hyper Hardware</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Jalan Kuala Krai, Kota Bharu</t>
+          <t>Sede citata a Sungai Pelong (stato non confermato)</t>
         </is>
       </c>
       <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>09-744 9555</t>
-        </is>
-      </c>
+      <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -4217,10 +4886,15 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Attività non confermata.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Catena ferramenta; presenza in Kelantan non confermata.</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4234,25 +4908,21 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>KB Genset</t>
+          <t>Hassan Abdullah Hardware Sdn. Bhd.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Jalan Mahmud, Kota Bharu</t>
+          <t>Ketereh (Kota Bharu)</t>
         </is>
       </c>
       <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>019-379 3191</t>
-        </is>
-      </c>
+      <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -4261,10 +4931,15 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Probabile generatori, attività non confermata.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Ferramenta generale, fondata 1983. Non chiaro se venda a clienti B2B industriali. 2° giro.</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4278,37 +4953,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>New Ah Piar Motor</t>
+          <t>SLS Kelantan Sdn. Bhd.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Kampung Wakar Che Yeh, Kota Bharu</t>
+          <t>Jalan Kuala Krai, Kota Bharu</t>
         </is>
       </c>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>09-748 1497</t>
+          <t>09-744 9555</t>
         </is>
       </c>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Probabile cliente finale</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Probabile officina/motori.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Attività non confermata.</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4327,20 +5007,16 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>SLS Kelantan Sdn. Bhd.</t>
+          <t>Hassan Abdullah Hardware Sdn. Bhd.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Jalan Kuala Krai, Kota Bharu</t>
+          <t>Ketereh (Kota Bharu)</t>
         </is>
       </c>
       <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>09-744 9555</t>
-        </is>
-      </c>
+      <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -4349,10 +5025,15 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Attività non confermata.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Ferramenta generale, fondata 1983. Non chiaro se venda a clienti B2B industriali. 2° giro.</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4361,42 +5042,47 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>iMEC Group of Companies</t>
+          <t>KB Genset</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Melaka e Kuantan</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>https://imec.com.my</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="n"/>
+          <t>Jalan Mahmud, Kota Bharu</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>019-379 3191</t>
+        </is>
+      </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Produttore di detergenti chimici.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Probabile generatori, attività non confermata.</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4405,38 +5091,47 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Multitech Industry Supplies</t>
+          <t>New Ah Piar Motor</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Taman Industri Malim Jaya, Melaka</t>
+          <t>Kampung Wakar Che Yeh, Kota Bharu</t>
         </is>
       </c>
       <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>09-748 1497</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Probabile cliente finale</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Strumenti di misura e collaudo di precisione.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Probabile officina/motori.</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4445,38 +5140,47 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Tiam Heng Machinery Sdn Bhd</t>
+          <t>SLS Kelantan Sdn. Bhd.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Jalan Kuala Krai, Kota Bharu</t>
         </is>
       </c>
       <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>09-744 9555</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Macchinari, hardware e utensili industriali dal 1993.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Attività non confermata.</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4490,33 +5194,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Cleaning</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Yee Tat Hardware Sdn Bhd</t>
+          <t>iMEC Group of Companies</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Jonker Street, Melaka</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n"/>
+          <t>Melaka e Kuantan</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>https://imec.com.my</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Dal 1980; probabile negozio al dettaglio.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Produttore di detergenti chimici.</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4530,17 +5243,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Leeden Powerweld Sdn Bhd</t>
+          <t>Multitech Industry Supplies</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Air Keroh, Melaka</t>
+          <t>Taman Industri Malim Jaya, Melaka</t>
         </is>
       </c>
       <c r="E23" s="3" t="n"/>
@@ -4548,15 +5261,20 @@
       <c r="G23" s="3" t="n"/>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Produttore di prodotti per saldatura (gruppo Leeden NOX).</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Strumenti di misura e collaudo di precisione. | VERIFICA: 30 Jalan IMJ 1, Taman Industri Malim Jaya, Melaka. Distributore esclusivo PRECISE e VIEW MASTER: strumenti di misura, non utensileria in senso stretto.</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4570,7 +5288,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4593,10 +5311,15 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Macchinari, hardware e utensili industriali dal 1993.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Macchinari, hardware e utensili industriali dal 1993. | VERIFICA: 146-B/C Jalan Kesidang 1/10, Bachang, Melaka. SSM 200501015289. Rivenditore generalista. Sito non trovato.</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4605,22 +5328,22 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Genesis Asia Sdn Bhd</t>
+          <t>Yee Tat Hardware Sdn Bhd</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Seremban 2</t>
+          <t>Jonker Street, Melaka</t>
         </is>
       </c>
       <c r="E25" s="3" t="n"/>
@@ -4628,15 +5351,20 @@
       <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Probabile cliente finale</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Impresa di servizi di pulizia: probabile cliente finale.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Dal 1980; probabile negozio al dettaglio.</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4645,42 +5373,43 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Pahang</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>KS Tools Depot (Malaysia)</t>
+          <t>Leeden Powerweld Sdn Bhd</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Perkampungan Setali, Kuantan</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>https://mall.lapasar.com/supplier-profile/ks-tools-depot-malaysia</t>
-        </is>
-      </c>
+          <t>Air Keroh, Melaka</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n"/>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Fornitore B2B wholesale (power tools, elettrico). Unico candidato locale in Pahang.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Produttore di prodotti per saldatura (gruppo Leeden NOX).</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4689,22 +5418,22 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Penang</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Chiptronics (M) Sdn. Bhd.</t>
+          <t>Tiam Heng Machinery Sdn Bhd</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Gelugor</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="E27" s="3" t="n"/>
@@ -4712,15 +5441,20 @@
       <c r="G27" s="3" t="n"/>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Attrezzature/utensili/adesivi industriali; da verificare se rivenditore.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Macchinari, hardware e utensili industriali dal 1993. | VERIFICA: 146-B/C Jalan Kesidang 1/10, Bachang, Melaka. SSM 200501015289. Rivenditore generalista. Sito non trovato.</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4729,22 +5463,22 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Penang</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Cleaning</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Alloytool (M) Sdn Bhd</t>
+          <t>Genesis Asia Sdn Bhd</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Perai</t>
+          <t>Seremban 2</t>
         </is>
       </c>
       <c r="E28" s="3" t="n"/>
@@ -4752,15 +5486,20 @@
       <c r="G28" s="3" t="n"/>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Probabile cliente finale</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Utensili da taglio in metallo duro, ceramica, CBN, PCD.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Impresa di servizi di pulizia: probabile cliente finale.</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4769,7 +5508,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Penang</t>
+          <t>Pahang</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4779,15 +5518,19 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Berjaya Hardware (B'Worth) Sdn Bhd</t>
+          <t>KS Tools Depot (Malaysia)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Butterworth</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n"/>
+          <t>Perkampungan Setali, Kuantan</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>https://mall.lapasar.com/supplier-profile/ks-tools-depot-malaysia</t>
+        </is>
+      </c>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
       <c r="H29" s="3" t="inlineStr">
@@ -4797,10 +5540,15 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Hardware industriale, macchinari, utensili. Dal 1983.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Fornitore B2B wholesale (power tools, elettrico). Unico candidato locale in Pahang. | VERIFICA: SSM 201303295436. Sito proprio non trovato. Il nome richiama il marchio tedesco KS Tools: verificare conflitto.</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4814,17 +5562,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Cleaning</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Dynarco Sdn Bhd</t>
+          <t>Chiptronics (M) Sdn. Bhd.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Perai</t>
+          <t>Gelugor</t>
         </is>
       </c>
       <c r="E30" s="3" t="n"/>
@@ -4832,15 +5580,20 @@
       <c r="G30" s="3" t="n"/>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Macchinari per precision tooling.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Attrezzature/utensili/adesivi industriali; da verificare se rivenditore.</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4859,12 +5612,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>EDM-Tools (Penang) Sdn Bhd</t>
+          <t>Alloytool (M) Sdn Bhd</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Penang</t>
+          <t>Perai</t>
         </is>
       </c>
       <c r="E31" s="3" t="n"/>
@@ -4877,10 +5630,15 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Materiali e accessori EDM, dal 1988.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Utensili da taglio in metallo duro, ceramica, CBN, PCD. | VERIFICA: 24-26 Lorong Nagasari 9, Taman Nagasari, Perai. Utensili da taglio. Dominio alloytool.com.my solo da riassunto di ricerca, da confermare. Marchi non verificati.</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4894,17 +5652,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Depolverazione</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Alloyplas Engineering Sdn Bhd</t>
+          <t>Berjaya Hardware (B'Worth) Sdn Bhd</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Penang</t>
+          <t>Butterworth</t>
         </is>
       </c>
       <c r="E32" s="3" t="n"/>
@@ -4912,15 +5670,20 @@
       <c r="G32" s="3" t="n"/>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Dust collector, fumi di saldatura: produttore/installatore.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Hardware industriale, macchinari, utensili. Dal 1983. | VERIFICA: Jalan Heng Choon Thian, Butterworth. Pagina Invest Penang non leggibile. Welding non confermato.</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4934,20 +5697,24 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Berjaya Hardware (B'Worth) Sdn Bhd</t>
+          <t>Dynarco Sdn Bhd</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Butterworth</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n"/>
+          <t>Perai</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>http://dynarco.com/</t>
+        </is>
+      </c>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
       <c r="H33" s="3" t="inlineStr">
@@ -4957,10 +5724,15 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Hardware industriale, macchinari, utensili. Dal 1983.</t>
+          <t>Confermato (riserva sul settore)</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Macchinari per precision tooling. | VERIFICA: 9 Jalan Todak 5, Seberang Jaya, Perai (+ Puchong). Piu macchine utensili (rettificatrici, EDM, CNC) che utensileria di consumo. Sito da riassunto di ricerca, non aperto.</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -4974,33 +5746,50 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Min Hardware &amp; Industrial Gases Sdn. Bhd.</t>
+          <t>EDM-Tools (Penang) Sdn Bhd</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Mak Mandin, Butterworth</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
+          <t>Penang</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>www.edmtools.com.my</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>+603-8062 5918 / +603-8060 3117 (numeri della sede Selangor)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>info@edmtools.com.my</t>
+        </is>
+      </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Gas industriali e attrezzature di saldatura. Dichiara di servire anche Kedah.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Materiali e accessori EDM, dal 1988. | VERIFICA: Sede a Prai (26 Lorong Nagasari 3). Produttore fili EDM in ottone e distributore esclusivo Erowa, Elbo Controlli, Thome, Toltec, Hwacheon; controllata di societa quotata.</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5014,17 +5803,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Depolverazione</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Berjaya Hardware (B'Worth) Sdn Bhd</t>
+          <t>Alloyplas Engineering Sdn Bhd</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Butterworth</t>
+          <t>Penang</t>
         </is>
       </c>
       <c r="E35" s="3" t="n"/>
@@ -5032,15 +5821,20 @@
       <c r="G35" s="3" t="n"/>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Hardware industriale, macchinari, utensili. Dal 1983.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Dust collector, fumi di saldatura: produttore/installatore.</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5054,17 +5848,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>EC Pneumatic &amp; Hardware Sdn Bhd</t>
+          <t>Berjaya Hardware (B'Worth) Sdn Bhd</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Jalan Chain Ferry, Perai</t>
+          <t>Butterworth</t>
         </is>
       </c>
       <c r="E36" s="3" t="n"/>
@@ -5077,10 +5871,15 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Componenti pneumatici e hardware.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware industriale, macchinari, utensili. Dal 1983. | VERIFICA: Jalan Heng Choon Thian, Butterworth. Pagina Invest Penang non leggibile. Welding non confermato.</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5094,17 +5893,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Textran Industries (Penang) Sdn Bhd</t>
+          <t>Min Hardware &amp; Industrial Gases Sdn. Bhd.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Penang</t>
+          <t>Mak Mandin, Butterworth</t>
         </is>
       </c>
       <c r="E37" s="3" t="n"/>
@@ -5117,10 +5916,15 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Distributore/stockist fasteners e ferramenta elettromeccanica.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Gas industriali e attrezzature di saldatura. Dichiara di servire anche Kedah. | VERIFICA: Dal 1984, Mak Mandin, Butterworth. Gas industriali + attrezzature e consumabili di saldatura. Pagina fonte non leggibile.</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5129,22 +5933,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Perak</t>
+          <t>Penang</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Wah Seng Sin Kee Co Sdn Bhd (WSSK)</t>
+          <t>Berjaya Hardware (B'Worth) Sdn Bhd</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Ipoh (filiali KL, Kuantan, Butterworth)</t>
+          <t>Butterworth</t>
         </is>
       </c>
       <c r="E38" s="3" t="n"/>
@@ -5157,10 +5961,15 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Distributore di ferramenta dagli anni cinquanta.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Hardware industriale, macchinari, utensili. Dal 1983. | VERIFICA: Jalan Heng Choon Thian, Butterworth. Pagina Invest Penang non leggibile. Welding non confermato.</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5169,42 +5978,51 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Perak</t>
+          <t>Penang</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>JESS Technology</t>
+          <t>EC Pneumatic &amp; Hardware Sdn Bhd</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Ipoh</t>
+          <t>Jalan Chain Ferry, Perai</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>https://www.jesstechnology.com</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n"/>
+          <t>https://ecpneumatic.com.my/</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>+604 380 1277 / 78; +6012 528 2779 (WhatsApp)</t>
+        </is>
+      </c>
       <c r="G39" s="3" t="n"/>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Riparazione saldatrici; vendita non confermata.</t>
+          <t>Confermato (settore pneumatica)</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>Componenti pneumatici e hardware. | VERIFICA: Email offuscata sul sito. Distributore dal 2006: SMC, Parker, Festo, Norgren, Camozzi, CKD; marchio proprio SWISH. Nessun conflitto diretto con Dupuy rilevato.</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5213,7 +6031,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Perak</t>
+          <t>Penang</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -5223,12 +6041,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Wah Seng Sin Kee Co Sdn Bhd (WSSK)</t>
+          <t>Textran Industries (Penang) Sdn Bhd</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Ipoh (filiali KL, Kuantan, Butterworth)</t>
+          <t>Penang</t>
         </is>
       </c>
       <c r="E40" s="3" t="n"/>
@@ -5241,10 +6059,15 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Distributore di ferramenta dagli anni cinquanta.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>Distributore/stockist fasteners e ferramenta elettromeccanica. | VERIFICA: 15 Jalan Industri Impian 1, Bukit Mertajam (filiale a Johor Bahru). Fondata 1998. Fasteners/ricambi: Meccanica solo in senso lato.</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5253,22 +6076,22 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Perlis</t>
+          <t>Perak</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Cleaning</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Bann Edar Sdn Bhd</t>
+          <t>Floormac (M) Sdn Bhd</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Jalan Kangar-Alor Setar, Kangar</t>
+          <t>Ipoh (citta dedotta, non confermata)</t>
         </is>
       </c>
       <c r="E41" s="3" t="n"/>
@@ -5276,15 +6099,20 @@
       <c r="G41" s="3" t="n"/>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Conflitto di marchio</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Forniture elettriche, non confermato.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Distributore autorizzato Nilfisk, RCM, FASA, 3M: conflitto di marchio probabile nel Cleaning. 2° giro.</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5293,22 +6121,22 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Perlis</t>
+          <t>Perak</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Siang Electrical Kangar</t>
+          <t>Wah Seng Sin Kee Co Sdn Bhd (WSSK)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Kangar Town</t>
+          <t>Ipoh (filiali KL, Kuantan, Butterworth)</t>
         </is>
       </c>
       <c r="E42" s="3" t="n"/>
@@ -5316,15 +6144,20 @@
       <c r="G42" s="3" t="n"/>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Probabile retail al dettaglio.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Distributore di ferramenta dagli anni cinquanta. | VERIFICA: TBK 365 Jalan Menglembu, Ipoh. Sito NON verificato (wssk.com.my era solo un'ipotesi dell'agente: non usare). Jobstore lo classifica come manifattura, ruolo da chiarire.</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5333,42 +6166,47 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Perak</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Powermax Trading &amp; Supplies</t>
+          <t>JESS Technology</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Inanam, Kota Kinabalu</t>
+          <t>Ipoh</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>https://mall.lapasar.com/supplier-profile/powermax-trading-supplies</t>
+          <t>https://www.jesstechnology.com</t>
         </is>
       </c>
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="n"/>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Utensili elettrici e batterie (Milwaukee). Probabile rivenditore.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Riparazione saldatrici; vendita non confermata.</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5377,22 +6215,22 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Perak</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Unimekar Metals</t>
+          <t>Wah Seng Sin Kee Co Sdn Bhd (WSSK)</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>KKIP, Kota Kinabalu</t>
+          <t>Ipoh (filiali KL, Kuantan, Butterworth)</t>
         </is>
       </c>
       <c r="E44" s="3" t="n"/>
@@ -5400,15 +6238,20 @@
       <c r="G44" s="3" t="n"/>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Probabile cliente finale</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Riparazioni e zincatura: officina/cliente finale.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Distributore di ferramenta dagli anni cinquanta. | VERIFICA: TBK 365 Jalan Menglembu, Ipoh. Sito NON verificato (wssk.com.my era solo un'ipotesi dell'agente: non usare). Jobstore lo classifica come manifattura, ruolo da chiarire.</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5417,7 +6260,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Perlis</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -5427,12 +6270,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>DoubleGain Industrial Supplies</t>
+          <t>Bann Edar Sdn Bhd</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Kolombong, Inanam, Kota Kinabalu</t>
+          <t>Jalan Kangar-Alor Setar, Kangar</t>
         </is>
       </c>
       <c r="E45" s="3" t="n"/>
@@ -5445,10 +6288,15 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Vetroresina, resine, pigmenti; fit debole.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Forniture elettriche, non confermato.</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5457,7 +6305,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Perlis</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -5467,20 +6315,16 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Summit Kinabalu Sdn Bhd</t>
+          <t>Siang Electrical Kangar</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Jalan Tuaran, Kota Kinabalu</t>
+          <t>Kangar Town</t>
         </is>
       </c>
       <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>+6088216946</t>
-        </is>
-      </c>
+      <c r="F46" s="3" t="n"/>
       <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="inlineStr">
         <is>
@@ -5489,10 +6333,15 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Ferramenta e vernici; fit con Dupuy debole.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Probabile retail al dettaglio.</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5506,33 +6355,42 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Unimekar Metals</t>
+          <t>Powermax Trading &amp; Supplies</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>KKIP, Kota Kinabalu</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n"/>
+          <t>Inanam, Kota Kinabalu</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>https://mall.lapasar.com/supplier-profile/powermax-trading-supplies</t>
+        </is>
+      </c>
       <c r="F47" s="3" t="n"/>
       <c r="G47" s="3" t="n"/>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Probabile cliente finale</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Riparazioni e zincatura: officina/cliente finale.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Utensili elettrici e batterie (Milwaukee). Probabile rivenditore. | VERIFICA: Lorong Mutiara Inanam, Kota Kinabalu. Vende Milwaukee: possibile conflitto. Solo profilo marketplace, attivita attuale non provata.</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5541,22 +6399,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Sarawak</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Sara Besi Hardware &amp; Engineering Sdn Bhd</t>
+          <t>Unimekar Metals</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Jln Padungan, Kuching</t>
+          <t>KKIP, Kota Kinabalu</t>
         </is>
       </c>
       <c r="E48" s="3" t="n"/>
@@ -5564,15 +6422,20 @@
       <c r="G48" s="3" t="n"/>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Probabile cliente finale</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Materiali edili ed elettroutensili (Makita, HiKOKI).</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>Riparazioni e zincatura: officina/cliente finale.</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5581,22 +6444,22 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Sarawak</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Sin Yew Seng Hardware &amp; Machineries Sdn Bhd</t>
+          <t>DoubleGain Industrial Supplies</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Khoo Peng Loong Road, Sibu</t>
+          <t>Kolombong, Inanam, Kota Kinabalu</t>
         </is>
       </c>
       <c r="E49" s="3" t="n"/>
@@ -5604,15 +6467,20 @@
       <c r="G49" s="3" t="n"/>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Grossista macchinari e attrezzature industriali dal 1990.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>Vetroresina, resine, pigmenti; fit debole.</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5621,42 +6489,47 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Sarawak</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Kiat Seng Welding Works Sdn Bhd</t>
+          <t>Summit Kinabalu Sdn Bhd</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Piasau Industrial Estate, Miri</t>
+          <t>Jalan Tuaran, Kota Kinabalu</t>
         </is>
       </c>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>085-656 212</t>
+          <t>+6088216946</t>
         </is>
       </c>
       <c r="G50" s="3" t="n"/>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Probabile cliente finale</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Probabile officina di saldatura.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>Ferramenta e vernici; fit con Dupuy debole.</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5665,42 +6538,43 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Sarawak</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Pan Sarawak Co Sdn Bhd (Pansar)</t>
+          <t>Unimekar Metals</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Sibu, Miri, Kuching</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>https://pansar.com.my</t>
-        </is>
-      </c>
+          <t>KKIP, Kota Kinabalu</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n"/>
       <c r="G51" s="3" t="n"/>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Probabile cliente finale</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Distributore Lincoln Electric per East Malaysia. Verificare eventuale conflitto di marca.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>Riparazioni e zincatura: officina/cliente finale.</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5714,17 +6588,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Miri Industrial Sdn Bhd</t>
+          <t>Sara Besi Hardware &amp; Engineering Sdn Bhd</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Piasau Business Park, Miri</t>
+          <t>Jln Padungan, Kuching</t>
         </is>
       </c>
       <c r="E52" s="3" t="n"/>
@@ -5732,15 +6606,20 @@
       <c r="G52" s="3" t="n"/>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Ricambi macchine movimento terra; probabilmente fuori target.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>Materiali edili ed elettroutensili (Makita, HiKOKI). | VERIFICA: 248 Teck Guan Building, Jalan Padungan, Kuching. Nessuna fonte su marchi o attivita corrente.</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5754,24 +6633,20 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Pan Sarawak Co Sdn Bhd (Pansar)</t>
+          <t>Sin Yew Seng Hardware &amp; Machineries Sdn Bhd</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Sibu, Miri, Kuching</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>https://pansar.com.my</t>
-        </is>
-      </c>
+          <t>Khoo Peng Loong Road, Sibu</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="n"/>
       <c r="G53" s="3" t="n"/>
       <c r="H53" s="3" t="inlineStr">
@@ -5781,10 +6656,15 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Distributore Lincoln Electric per East Malaysia. Verificare eventuale conflitto di marca.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>Grossista macchinari e attrezzature industriali dal 1990. | VERIFICA: Dati 2024 indicano attivita recente. Marchi e settore non verificati.</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5798,33 +6678,42 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Sin Yew Seng Hardware &amp; Machineries Sdn Bhd</t>
+          <t>Kiat Seng Welding Works Sdn Bhd</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Khoo Peng Loong Road, Sibu</t>
+          <t>Piasau Industrial Estate, Miri</t>
         </is>
       </c>
       <c r="E54" s="3" t="n"/>
-      <c r="F54" s="3" t="n"/>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>085-656 212</t>
+        </is>
+      </c>
       <c r="G54" s="3" t="n"/>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Probabile cliente finale</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Grossista macchinari e attrezzature industriali dal 1990.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>Probabile officina di saldatura.</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5833,38 +6722,47 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sarawak</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Duromac (M) Sdn Bhd</t>
+          <t>Pan Sarawak Co Sdn Bhd (Pansar)</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Puchong</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n"/>
+          <t>Sibu, Miri, Kuching</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>https://pansar.com.my/</t>
+        </is>
+      </c>
       <c r="F55" s="3" t="n"/>
       <c r="G55" s="3" t="n"/>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Conflitto di marchio</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Spazzatrici; rappresenta DISAB-TELLA (aspiratori industriali).</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>Distributore Lincoln Electric per East Malaysia. Verificare eventuale conflitto di marca. | VERIFICA: 23 Jalan Bengkel, Sibu. Dal 1961. DISTRIBUTORE ESCLUSIVO Lincoln Electric da 30+ anni (marchi Arcweld, Duraweld, Optimarc...): conflitto probabile nel Welding. Pagina contatti non aperta.</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5873,22 +6771,22 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sarawak</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Klenco (M) Sdn Bhd</t>
+          <t>Miri Industrial Sdn Bhd</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Bukit Naga Industrial Park</t>
+          <t>Piasau Business Park, Miri</t>
         </is>
       </c>
       <c r="E56" s="3" t="n"/>
@@ -5901,10 +6799,15 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Tipo di prodotto non chiaro.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>Ricambi macchine movimento terra; probabilmente fuori target.</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5913,38 +6816,47 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sarawak</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Kärcher Cleaning Systems Sdn Bhd</t>
+          <t>Pan Sarawak Co Sdn Bhd (Pansar)</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="n"/>
+          <t>Sibu, Miri, Kuching</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>https://pansar.com.my/</t>
+        </is>
+      </c>
       <c r="F57" s="3" t="n"/>
       <c r="G57" s="3" t="n"/>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Conflitto di marchio</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Filiale di produttore.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Distributore Lincoln Electric per East Malaysia. Verificare eventuale conflitto di marca. | VERIFICA: 23 Jalan Bengkel, Sibu. Dal 1961. DISTRIBUTORE ESCLUSIVO Lincoln Electric da 30+ anni (marchi Arcweld, Duraweld, Optimarc...): conflitto probabile nel Welding. Pagina contatti non aperta.</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -5953,29 +6865,25 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sarawak</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Techno Tools &amp; Equipment</t>
+          <t>Sin Yew Seng Hardware &amp; Machineries Sdn Bhd</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Ampang</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>https://techno.my</t>
-        </is>
-      </c>
+          <t>Khoo Peng Loong Road, Sibu</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n"/>
       <c r="G58" s="3" t="n"/>
       <c r="H58" s="3" t="inlineStr">
@@ -5985,10 +6893,15 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Fornitore autorizzato Kärcher; potrebbe essere più un retailer.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Grossista macchinari e attrezzature industriali dal 1990. | VERIFICA: Dati 2024 indicano attivita recente. Marchi e settore non verificati.</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6007,32 +6920,41 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>XTS Technologies Sdn Bhd</t>
+          <t>Duromac (M) Sdn Bhd</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Taman Industri Meranti Jaya, Puchong</t>
+          <t>Puchong</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>https://www.plantautomation-technology.com/suppliers/xts-technologies-sdn-bhd</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n"/>
+          <t>https://www.duromac.com (dal risultato di ricerca, non aperto)</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>+60 3 8070 2826 (da risultato di ricerca, non verificato sul sito)</t>
+        </is>
+      </c>
       <c r="G59" s="3" t="n"/>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Parts cleaning e ultrasuoni.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Spazzatrici; rappresenta DISAB-TELLA (aspiratori industriali). | VERIFICA: No.9 Jalan BK 1/15, Bandar Kinrara, Puchong. Dal 1996. Rivende spazzatrici di marchi terzi; nulla su depolverazione/aspirazione.</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6046,17 +6968,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Cleaning</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Aik Huat Hardware Trading Sdn Bhd</t>
+          <t>Klenco (M) Sdn Bhd</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Klang Valley</t>
+          <t>Bukit Naga Industrial Park</t>
         </is>
       </c>
       <c r="E60" s="3" t="n"/>
@@ -6069,10 +6991,15 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>Edilizia ed elettroutensili, forse poco industriale.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Tipo di prodotto non chiaro.</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6086,17 +7013,17 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Cleaning</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>C-MART &amp; BUDDY TOOLS</t>
+          <t>Kärcher Cleaning Systems Sdn Bhd</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Non chiara</t>
+          <t>Shah Alam</t>
         </is>
       </c>
       <c r="E61" s="3" t="n"/>
@@ -6104,15 +7031,20 @@
       <c r="G61" s="3" t="n"/>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Probabile entità indonesiana; legame con Malesia incerto.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Filiale di produttore.</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6126,26 +7058,34 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Cleaning</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>CT Hardware</t>
+          <t>Techno Tools &amp; Equipment</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Petaling Jaya</t>
+          <t>Ampang</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>https://cthardware.com</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="n"/>
-      <c r="G62" s="3" t="n"/>
+          <t>https://techno.my</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>+603-4270 2333</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>sales@techno.com.my</t>
+        </is>
+      </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -6153,10 +7093,15 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>Distributore ventilatori, soffianti, saldatrici.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Fornitore autorizzato Kärcher; potrebbe essere più un retailer. | VERIFICA: 36-1 Jalan Sulaiman 1, Taman Putra Sulaiman, Ampang. Distributore dal 2007, 50+ marchi. CONFLITTI: Karcher (cleaning), DeWalt, Bosch, Makita, Stanley. Generalista MRO.</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6170,33 +7115,42 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Cleaning</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Dian Be Hardware Co Sdn Bhd</t>
+          <t>XTS Technologies Sdn Bhd</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Petaling Jaya</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n"/>
+          <t>Taman Industri Meranti Jaya, Puchong</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.plantautomation-technology.com/suppliers/xts-technologies-sdn-bhd</t>
+        </is>
+      </c>
       <c r="F63" s="3" t="n"/>
       <c r="G63" s="3" t="n"/>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Ferramenta e utensili.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Parts cleaning e ultrasuoni.</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6215,12 +7169,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>HLH Welding Supply</t>
+          <t>Aik Huat Hardware Trading Sdn Bhd</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Klang</t>
+          <t>Klang Valley</t>
         </is>
       </c>
       <c r="E64" s="3" t="n"/>
@@ -6228,15 +7182,20 @@
       <c r="G64" s="3" t="n"/>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Abrasivi, utensili, gas, saldatura, compressori.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>Edilizia ed elettroutensili, forse poco industriale.</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6255,32 +7214,33 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Techno Tools &amp; Equipment</t>
+          <t>C-MART &amp; BUDDY TOOLS</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Ampang</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>https://techno.my</t>
-        </is>
-      </c>
+          <t>Non chiara</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n"/>
       <c r="F65" s="3" t="n"/>
       <c r="G65" s="3" t="n"/>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Fornitore autorizzato Kärcher; potrebbe essere più un retailer.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>Probabile entità indonesiana; legame con Malesia incerto.</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6299,17 +7259,29 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Tools &amp; Machinery Parts Supplies Sdn Bhd (TMP)</t>
+          <t>CT Hardware</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Seksyen 51A, Petaling Jaya</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n"/>
-      <c r="F66" s="3" t="n"/>
-      <c r="G66" s="3" t="n"/>
+          <t>Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>https://cthardware.com</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>(603) 7873 0000</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>hello@cthardware.com</t>
+        </is>
+      </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -6317,10 +7289,15 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Fornitore industriale dal 1984.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>Distributore ventilatori, soffianti, saldatrici. | VERIFICA: No.1 Jalan SS2/3, Petaling Jaya. Dal 1977, punti vendita Klang Valley. CONFLITTI: Karcher, Bosch, DeWalt, Makita, Graco; marchi propri Kawa, Welflo, Accubit. Profilo anche DIY/retail.</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6334,37 +7311,38 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Depolverazione</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Atlas Copco Malaysia</t>
+          <t>Dian Be Hardware Co Sdn Bhd</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>https://atlascopco.com/en-my</t>
-        </is>
-      </c>
+          <t>Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n"/>
       <c r="F67" s="3" t="n"/>
       <c r="G67" s="3" t="n"/>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Multinazionale del vuoto, non idonea come distributore.</t>
+          <t>Non verificabile</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>Ferramenta e utensili. | VERIFICA: Solo directory a bassa affidabilita; negozio ferramenta/DIY, 2 Jalan SS 2/63, PJ.</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6378,37 +7356,38 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Depolverazione</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>DAV Engineering Sdn Bhd</t>
+          <t>HLH Welding Supply</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>https://www.exporthub.com/dav-engineering-sdn-bhd/</t>
-        </is>
-      </c>
+          <t>Klang</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n"/>
       <c r="F68" s="3" t="n"/>
       <c r="G68" s="3" t="n"/>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Produttore di dust collector e ventilatori.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>Abrasivi, utensili, gas, saldatura, compressori. | VERIFICA: Klang. Saldatura, abrasivi, utensili, compressori, idropulitrici, gas. Dominio/contatti non verificati. Forse collegata a HLH Industrial Supply (M) Sdn Bhd (non provato).</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6422,22 +7401,34 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Depolverazione</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Duromac (M) Sdn Bhd</t>
+          <t>Techno Tools &amp; Equipment</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Puchong</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n"/>
-      <c r="F69" s="3" t="n"/>
-      <c r="G69" s="3" t="n"/>
+          <t>Ampang</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>https://techno.my</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>+603-4270 2333</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>sales@techno.com.my</t>
+        </is>
+      </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -6445,10 +7436,15 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Spazzatrici; rappresenta DISAB-TELLA (aspiratori industriali).</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>Fornitore autorizzato Kärcher; potrebbe essere più un retailer. | VERIFICA: 36-1 Jalan Sulaiman 1, Taman Putra Sulaiman, Ampang. Distributore dal 2007, 50+ marchi. CONFLITTI: Karcher (cleaning), DeWalt, Bosch, Makita, Stanley. Generalista MRO.</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6462,33 +7458,42 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Depolverazione</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Singuan Blasting Sdn Bhd</t>
+          <t>Tools &amp; Machinery Parts Supplies Sdn Bhd (TMP)</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n"/>
+          <t>Seksyen 51A, Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>https://tomac.com.my (compare nei risultati; /about 404, non aperto)</t>
+        </is>
+      </c>
       <c r="F70" s="3" t="n"/>
       <c r="G70" s="3" t="n"/>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>Costruisce sabbiatrici e depolveratori.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>Fornitore industriale dal 1984. | VERIFICA: Lot 22 Jalan 51A/223, PJ 46100. Dal 1984. Utensili manuali, torque, sollevamento, pneumatici, MRO oil&amp;gas. Marchi non verificati.</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6502,33 +7507,42 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>ATEX</t>
+          <t>Depolverazione</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Ampmech Sdn Bhd</t>
+          <t>Atlas Copco Malaysia</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Damansara Jaya, Petaling Jaya</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n"/>
+          <t>Shah Alam</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>https://atlascopco.com/en-my</t>
+        </is>
+      </c>
       <c r="F71" s="3" t="n"/>
       <c r="G71" s="3" t="n"/>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Channel partner Ceag, Rittal, Mennekes; uffici anche a Penang, Bintulu, Miri.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>Multinazionale del vuoto, non idonea come distributore.</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6542,22 +7556,22 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>ATEX</t>
+          <t>Depolverazione</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Beckhoff Automation Sdn Bhd</t>
+          <t>DAV Engineering Sdn Bhd</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Kota Damansara</t>
+          <t>Shah Alam</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>https://beckhoff.com</t>
+          <t>https://www.exporthub.com/dav-engineering-sdn-bhd/</t>
         </is>
       </c>
       <c r="F72" s="3" t="n"/>
@@ -6569,10 +7583,15 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>Produttore di automazione: da escludere.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>Produttore di dust collector e ventilatori.</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6586,21 +7605,29 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>ATEX</t>
+          <t>Depolverazione</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>See Kwong Electric (KL) Sdn Bhd</t>
+          <t>Duromac (M) Sdn Bhd</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Puchong (Jalan TPP 5/2)</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
+          <t>Puchong</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>https://www.duromac.com (dal risultato di ricerca, non aperto)</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>+60 3 8070 2826 (da risultato di ricerca, non verificato sul sito)</t>
+        </is>
+      </c>
       <c r="G73" s="3" t="n"/>
       <c r="H73" s="3" t="inlineStr">
         <is>
@@ -6609,10 +7636,15 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Prodotti antideflagranti ATEX/IECEx, attiva dal 1982.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>Spazzatrici; rappresenta DISAB-TELLA (aspiratori industriali). | VERIFICA: No.9 Jalan BK 1/15, Bandar Kinrara, Puchong. Dal 1996. Rivende spazzatrici di marchi terzi; nulla su depolverazione/aspirazione.</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6626,33 +7658,42 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Sabbiatura</t>
+          <t>Depolverazione</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Medias Industrial Supplies Sdn Bhd</t>
+          <t>Master Jaya Environment Sdn Bhd</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
+          <t>Taming Jaya Industrial Park, Seri Kembangan</t>
         </is>
       </c>
       <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>+60389626233</t>
+        </is>
+      </c>
       <c r="G74" s="3" t="n"/>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>Dal 1986: abrasivi, cabine, granigliatrici, ricambi.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>Controllo inquinamento aria, ventilazione, fume cleaning: contractor/produttore, priorita bassa. 2° giro.</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6666,17 +7707,17 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Sabbiatura</t>
+          <t>Depolverazione</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Schmidt Abrasive Blasting</t>
+          <t>Singuan Blasting Sdn Bhd</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Petaling Jaya</t>
+          <t>Shah Alam</t>
         </is>
       </c>
       <c r="E75" s="3" t="n"/>
@@ -6684,15 +7725,20 @@
       <c r="G75" s="3" t="n"/>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>Conflitto di marchio</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Distributore marchio Schmidt, dal 2012: probabile conflitto di marca.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>Costruisce sabbiatrici e depolveratori.</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6706,33 +7752,50 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Sabbiatura</t>
+          <t>ATEX</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Singuan Blasting Sdn Bhd</t>
+          <t>Ampmech Sdn Bhd</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
+          <t>Damansara Jaya, Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ampmech.com</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>+603-7728 6250 / +6016-718 6250</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>info@ampmech.com</t>
+        </is>
+      </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>Costruisce sabbiatrici e depolveratori.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>Channel partner Ceag, Rittal, Mennekes; uffici anche a Penang, Bintulu, Miri. | VERIFICA: 46 Jalan SS22/21, Damansara Jaya. Stocking distributor prodotti Ex; ISO 9001; sedi anche a Kemaman, Bintulu, Miri, Penang. Marchi: Eaton Crouse-Hinds, CEAG, Thuba, Mennekes, Gewiss, Rittal, Fluke.</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6746,33 +7809,42 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>ATEX</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>C-MART &amp; BUDDY TOOLS</t>
+          <t>Beckhoff Automation Sdn Bhd</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Non chiara</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n"/>
+          <t>Kota Damansara</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>https://beckhoff.com</t>
+        </is>
+      </c>
       <c r="F77" s="3" t="n"/>
       <c r="G77" s="3" t="n"/>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Probabile entità indonesiana; legame con Malesia incerto.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>Produttore di automazione: da escludere.</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6786,24 +7858,20 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>ATEX</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>CT Hardware</t>
+          <t>See Kwong Electric (KL) Sdn Bhd</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Petaling Jaya</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>https://cthardware.com</t>
-        </is>
-      </c>
+          <t>Puchong (Jalan TPP 5/2)</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n"/>
       <c r="G78" s="3" t="n"/>
       <c r="H78" s="3" t="inlineStr">
@@ -6813,10 +7881,15 @@
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>Distributore ventilatori, soffianti, saldatrici.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Prodotti antideflagranti ATEX/IECEx, attiva dal 1982. | VERIFICA: 14 &amp; 16 Jalan TPP 5/2, Puchong. SSM 87458-A, dal 1982. Stockist ATEX/IECEx. Dominio/contatti non confermati.</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6830,17 +7903,17 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Sabbiatura</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>HLH Welding Supply</t>
+          <t>Medias Industrial Supplies Sdn Bhd</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Klang</t>
+          <t>Shah Alam</t>
         </is>
       </c>
       <c r="E79" s="3" t="n"/>
@@ -6853,10 +7926,15 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Abrasivi, utensili, gas, saldatura, compressori.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>Dal 1986: abrasivi, cabine, granigliatrici, ricambi. | VERIFICA: Shah Alam. Fonte principale: scheda directory indonesiana (identita/indirizzo da riverificare). Ruolo distributore/produttore non chiaro.</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6870,17 +7948,17 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Sabbiatura</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>MECHKINARC (M) Sdn Bhd</t>
+          <t>Schmidt Abrasive Blasting</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
+          <t>Petaling Jaya</t>
         </is>
       </c>
       <c r="E80" s="3" t="n"/>
@@ -6888,15 +7966,20 @@
       <c r="G80" s="3" t="n"/>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Conflitto di marchio</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>Macchine taglio e saldatura marchio MORROW.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>Distributore marchio Schmidt, dal 2012: probabile conflitto di marca.</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6910,37 +7993,38 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Sabbiatura</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Techno Tools &amp; Equipment</t>
+          <t>Singuan Blasting Sdn Bhd</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Ampang</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>https://techno.my</t>
-        </is>
-      </c>
+          <t>Shah Alam</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n"/>
       <c r="F81" s="3" t="n"/>
       <c r="G81" s="3" t="n"/>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>Fornitore autorizzato Kärcher; potrebbe essere più un retailer.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>Costruisce sabbiatrici e depolveratori.</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6959,12 +8043,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>TSIS Welding Solution Sdn Bhd</t>
+          <t>C-MART &amp; BUDDY TOOLS</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Selangor (città n.d.)</t>
+          <t>Non chiara</t>
         </is>
       </c>
       <c r="E82" s="3" t="n"/>
@@ -6972,15 +8056,20 @@
       <c r="G82" s="3" t="n"/>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>Conflitto di marchio</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>Distributore esclusivo Fronius dal 2015.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>Probabile entità indonesiana; legame con Malesia incerto.</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -6999,28 +8088,45 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>TSM Welding Technology Sdn Bhd</t>
+          <t>CT Hardware</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Klang</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
-      <c r="G83" s="3" t="n"/>
+          <t>Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>https://cthardware.com</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>(603) 7873 0000</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>hello@cthardware.com</t>
+        </is>
+      </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>Saldatura a resistenza: nicchia.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>Distributore ventilatori, soffianti, saldatrici. | VERIFICA: No.1 Jalan SS2/3, Petaling Jaya. Dal 1977, punti vendita Klang Valley. CONFLITTI: Karcher, Bosch, DeWalt, Makita, Graco; marchi propri Kawa, Welflo, Accubit. Profilo anche DIY/retail.</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7039,12 +8145,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Weld Systems Sdn Bhd</t>
+          <t>HLH Welding Supply</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Petaling Jaya</t>
+          <t>Klang</t>
         </is>
       </c>
       <c r="E84" s="3" t="n"/>
@@ -7057,10 +8163,15 @@
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>Vendita, noleggio e riparazione saldatrici e plasma.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>Abrasivi, utensili, gas, saldatura, compressori. | VERIFICA: Klang. Saldatura, abrasivi, utensili, compressori, idropulitrici, gas. Dominio/contatti non verificati. Forse collegata a HLH Industrial Supply (M) Sdn Bhd (non provato).</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7074,37 +8185,38 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>CT Hardware</t>
+          <t>MECHKINARC (M) Sdn Bhd</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Petaling Jaya</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>https://cthardware.com</t>
-        </is>
-      </c>
+          <t>Shah Alam</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n"/>
       <c r="F85" s="3" t="n"/>
       <c r="G85" s="3" t="n"/>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Conflitto di marchio</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>Distributore ventilatori, soffianti, saldatrici.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>Macchine taglio e saldatura marchio MORROW. | VERIFICA: No.7 Jalan Dermawan 25/89, Shah Alam. Agente esclusivo marchio MORROW (taglio/saldatura): conflitto di marca nel Welding.</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7118,37 +8230,50 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>DAV Engineering Sdn Bhd</t>
+          <t>Techno Tools &amp; Equipment</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
+          <t>Ampang</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>https://www.exporthub.com/dav-engineering-sdn-bhd/</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="n"/>
-      <c r="G86" s="3" t="n"/>
+          <t>https://techno.my</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>+603-4270 2333</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>sales@techno.com.my</t>
+        </is>
+      </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>Produttore di dust collector e ventilatori.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>Fornitore autorizzato Kärcher; potrebbe essere più un retailer. | VERIFICA: 36-1 Jalan Sulaiman 1, Taman Putra Sulaiman, Ampang. Distributore dal 2007, 50+ marchi. CONFLITTI: Karcher (cleaning), DeWalt, Bosch, Makita, Stanley. Generalista MRO.</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7162,17 +8287,17 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Elta Fans Malaysia Sdn Bhd</t>
+          <t>TSIS Welding Solution Sdn Bhd</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Shah Alam</t>
+          <t>Selangor (città n.d.)</t>
         </is>
       </c>
       <c r="E87" s="3" t="n"/>
@@ -7180,15 +8305,20 @@
       <c r="G87" s="3" t="n"/>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Conflitto di marchio</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>Vendita e distribuzione ventilatori.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>Distributore esclusivo Fronius dal 2015.</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7202,41 +8332,38 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Systemair Malaysia</t>
+          <t>TSM Welding Technology Sdn Bhd</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Kampung Jaya, Selangor 47000</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>https://www.systemair.my</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>603-6157 1177</t>
-        </is>
-      </c>
+          <t>Klang</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
       <c r="G88" s="3" t="n"/>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>Probabile costruttore/filiale (ventilazione).</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>Saldatura a resistenza: nicchia.</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7250,17 +8377,17 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Tools &amp; Machinery Parts Supplies Sdn Bhd (TMP)</t>
+          <t>Weld Systems Sdn Bhd</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Seksyen 51A, Petaling Jaya</t>
+          <t>Petaling Jaya</t>
         </is>
       </c>
       <c r="E89" s="3" t="n"/>
@@ -7273,10 +8400,15 @@
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>Fornitore industriale dal 1984.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>Vendita, noleggio e riparazione saldatrici e plasma. | VERIFICA: 45 Jalan PJU 1A/18, Taman Perindustrian Jaya, PJ. Vende, noleggia, ripara saldatrici. Sito/contatti non verificati.</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7295,28 +8427,45 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Vostermans Ventilation Sdn Bhd</t>
+          <t>CT Hardware</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Klang</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" s="3" t="n"/>
-      <c r="G90" s="3" t="n"/>
+          <t>Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>https://cthardware.com</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>(603) 7873 0000</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>hello@cthardware.com</t>
+        </is>
+      </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>Probabile costruttore.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>Distributore ventilatori, soffianti, saldatrici. | VERIFICA: No.1 Jalan SS2/3, Petaling Jaya. Dal 1977, punti vendita Klang Valley. CONFLITTI: Karcher, Bosch, DeWalt, Makita, Graco; marchi propri Kawa, Welflo, Accubit. Profilo anche DIY/retail.</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7325,42 +8474,47 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Sede non determinata / nazionale</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Lapasar (marketplace B2B MRO)</t>
+          <t>DAV Engineering Sdn Bhd</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Consegna nazionale</t>
+          <t>Shah Alam</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>https://lapasar.com</t>
+          <t>https://www.exporthub.com/dav-engineering-sdn-bhd/</t>
         </is>
       </c>
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="3" t="n"/>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>Aggregatore con 10.000+ fornitori, non distributore diretto. Compare nei risultati di quasi tutti gli stati.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>Produttore di dust collector e ventilatori.</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7369,42 +8523,43 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Sede non determinata / nazionale</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>UMW (Holdings / Equipment)</t>
+          <t>Elta Fans Malaysia Sdn Bhd</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Non indicata</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>https://simeumw.com</t>
-        </is>
-      </c>
+          <t>Shah Alam</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n"/>
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>Conflitto di marchio</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>Rappresenta Tennant: probabile conflitto di marca.</t>
+          <t>Scartato</t>
         </is>
       </c>
       <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>Vendita e distribuzione ventilatori. | VERIFICA: SCARTATO dopo verifica: produttore (filiale gruppo Elta), non distributore.</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7413,42 +8568,43 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Sede non determinata / nazionale</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Guhring Malaysia Sdn Bhd</t>
+          <t>Luchtech Engineering Sdn Bhd</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Presenza a Penang non confermata</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>https://malaysia.ahk.de/en/members/members-directory/guhring-malaysia-sdn-bhd</t>
-        </is>
-      </c>
+          <t>Jalan Utama 2/18, Puchong</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n"/>
       <c r="F93" s="3" t="n"/>
       <c r="G93" s="3" t="n"/>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>Produttore / possibile concorrente</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>Filiale di produttore.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>Aria compressa (compressori, essiccatori, filtri): settore marginale, solo come partner adiacente. 2° giro.</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7457,38 +8613,51 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Sede non determinata / nazionale</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Iklim Hardware &amp; Machinery</t>
+          <t>Systemair Malaysia</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Sede non confermata</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="n"/>
-      <c r="F94" s="3" t="n"/>
+          <t>Kampung Jaya, Selangor 47000</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.systemair.my</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>603-6157 1177</t>
+        </is>
+      </c>
       <c r="G94" s="3" t="n"/>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>Dichiara 50 anni di attività; sede non chiara.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>Probabile costruttore/filiale (ventilazione).</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7497,42 +8666,47 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Sede non determinata / nazionale</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Lapasar (marketplace B2B MRO)</t>
+          <t>Tools &amp; Machinery Parts Supplies Sdn Bhd (TMP)</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Consegna nazionale</t>
+          <t>Seksyen 51A, Petaling Jaya</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>https://lapasar.com</t>
+          <t>https://tomac.com.my (compare nei risultati; /about 404, non aperto)</t>
         </is>
       </c>
       <c r="F95" s="3" t="n"/>
       <c r="G95" s="3" t="n"/>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Candidato</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>Aggregatore con 10.000+ fornitori, non distributore diretto. Compare nei risultati di quasi tutti gli stati.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>Fornitore industriale dal 1984. | VERIFICA: Lot 22 Jalan 51A/223, PJ 46100. Dal 1984. Utensili manuali, torque, sollevamento, pneumatici, MRO oil&amp;gas. Marchi non verificati.</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7541,42 +8715,43 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Sede non determinata / nazionale</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Utensileria</t>
+          <t>Meccanica</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>MBJ Bina Jaya Machinery &amp; Hardware Sdn Bhd</t>
+          <t>Vostermans Ventilation Sdn Bhd</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Sede non confermata (Sabah o Sarawak)</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>https://mall.lapasar.com/supplier-profile/mbj-bina-jaya-machinery-hardware</t>
-        </is>
-      </c>
+          <t>Klang</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n"/>
       <c r="F96" s="3" t="n"/>
       <c r="G96" s="3" t="n"/>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>Compare per Kota Kinabalu e Sarawak; sede non confermata.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>Probabile costruttore.</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7590,37 +8765,42 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>ATEX</t>
+          <t>Cleaning</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>GTE (Malaysia) / GTE Lighting &amp; Equipment</t>
+          <t>Lapasar (marketplace B2B MRO)</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Sede non verificata</t>
+          <t>Consegna nazionale</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>https://gte.com.my</t>
+          <t>https://lapasar.com</t>
         </is>
       </c>
       <c r="F97" s="3" t="n"/>
       <c r="G97" s="3" t="n"/>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>Illuminazione antideflagrante, distributore dal 2004.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>Aggregatore con 10.000+ fornitori, non distributore diretto. Compare nei risultati di quasi tutti gli stati.</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7634,33 +8814,42 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Sabbiatura</t>
+          <t>Cleaning</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Asia Airblast</t>
+          <t>UMW (Holdings / Equipment)</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Sede non indicata</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="n"/>
+          <t>Non indicata</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>https://simeumw.com</t>
+        </is>
+      </c>
       <c r="F98" s="3" t="n"/>
       <c r="G98" s="3" t="n"/>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Conflitto di marchio</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
         <is>
-          <t>Sede non determinata.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>Rappresenta Tennant: probabile conflitto di marca.</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7674,37 +8863,42 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Lapasar (marketplace B2B MRO)</t>
+          <t>Guhring Malaysia Sdn Bhd</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Consegna nazionale</t>
+          <t>Presenza a Penang non confermata</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>https://lapasar.com</t>
+          <t>https://malaysia.ahk.de/en/members/members-directory/guhring-malaysia-sdn-bhd</t>
         </is>
       </c>
       <c r="F99" s="3" t="n"/>
       <c r="G99" s="3" t="n"/>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>Aggregatore con 10.000+ fornitori, non distributore diretto. Compare nei risultati di quasi tutti gli stati.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>Filiale di produttore.</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7718,17 +8912,17 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>AMICO Bearings (M) Sdn Bhd</t>
+          <t>Iklim Hardware &amp; Machinery</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Rete nazionale</t>
+          <t>Sede non confermata</t>
         </is>
       </c>
       <c r="E100" s="3" t="n"/>
@@ -7741,10 +8935,15 @@
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>Stockist dal 1993; filiale in Kedah non confermata.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>Dichiara 50 anni di attività; sede non chiara.</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7758,33 +8957,42 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Iklim Hardware &amp; Machinery</t>
+          <t>Lapasar (marketplace B2B MRO)</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Sede non confermata</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="n"/>
+          <t>Consegna nazionale</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>https://lapasar.com</t>
+        </is>
+      </c>
       <c r="F101" s="3" t="n"/>
       <c r="G101" s="3" t="n"/>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>Debole / da verificare</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>Dichiara 50 anni di attività; sede non chiara.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>Aggregatore con 10.000+ fornitori, non distributore diretto. Compare nei risultati di quasi tutti gli stati.</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7798,37 +9006,42 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Lapasar (marketplace B2B MRO)</t>
+          <t>MBJ Bina Jaya Machinery &amp; Hardware Sdn Bhd</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Consegna nazionale</t>
+          <t>Sede non confermata (Sabah o Sarawak)</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>https://lapasar.com</t>
+          <t>https://mall.lapasar.com/supplier-profile/mbj-bina-jaya-machinery-hardware</t>
         </is>
       </c>
       <c r="F102" s="3" t="n"/>
       <c r="G102" s="3" t="n"/>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>Aggregatore con 10.000+ fornitori, non distributore diretto. Compare nei risultati di quasi tutti gli stati.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>Compare per Kota Kinabalu e Sarawak; sede non confermata.</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -7842,22 +9055,22 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>ATEX</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>MBJ Bina Jaya Machinery &amp; Hardware Sdn Bhd</t>
+          <t>GTE (Malaysia) / GTE Lighting &amp; Equipment</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Sede non confermata (Sabah o Sarawak)</t>
+          <t>Sede non verificata</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>https://mall.lapasar.com/supplier-profile/mbj-bina-jaya-machinery-hardware</t>
+          <t>https://gte.com.my</t>
         </is>
       </c>
       <c r="F103" s="3" t="n"/>
@@ -7869,17 +9082,304 @@
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>Illuminazione antideflagrante, distributore dal 2004.</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>DA VERIFICARE UMANAMENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Sede non determinata / nazionale</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Sabbiatura</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Asia Airblast</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Sede non indicata</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n"/>
+      <c r="F104" s="3" t="n"/>
+      <c r="G104" s="3" t="n"/>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>Debole / da verificare</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>Sede non determinata.</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>DA VERIFICARE UMANAMENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Sede non determinata / nazionale</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Welding</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Lapasar (marketplace B2B MRO)</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Consegna nazionale</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>https://lapasar.com</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="n"/>
+      <c r="G105" s="3" t="n"/>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>Aggregatore con 10.000+ fornitori, non distributore diretto. Compare nei risultati di quasi tutti gli stati.</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>DA VERIFICARE UMANAMENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>Sede non determinata / nazionale</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Meccanica</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>AMICO Bearings (M) Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Rete nazionale</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n"/>
+      <c r="F106" s="3" t="n"/>
+      <c r="G106" s="3" t="n"/>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>Debole / da verificare</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>Stockist dal 1993; filiale in Kedah non confermata.</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>DA VERIFICARE UMANAMENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Sede non determinata / nazionale</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Meccanica</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Iklim Hardware &amp; Machinery</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Sede non confermata</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n"/>
+      <c r="F107" s="3" t="n"/>
+      <c r="G107" s="3" t="n"/>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>Debole / da verificare</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>Dichiara 50 anni di attività; sede non chiara.</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>DA VERIFICARE UMANAMENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>Sede non determinata / nazionale</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Meccanica</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Lapasar (marketplace B2B MRO)</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Consegna nazionale</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>https://lapasar.com</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="n"/>
+      <c r="G108" s="3" t="n"/>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>Aggregatore con 10.000+ fornitori, non distributore diretto. Compare nei risultati di quasi tutti gli stati.</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>DA VERIFICARE UMANAMENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>Sede non determinata / nazionale</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>Meccanica</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>MBJ Bina Jaya Machinery &amp; Hardware Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Sede non confermata (Sabah o Sarawak)</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>https://mall.lapasar.com/supplier-profile/mbj-bina-jaya-machinery-hardware</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="n"/>
+      <c r="G109" s="3" t="n"/>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>Debole / da verificare</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
           <t>Compare per Kota Kinabalu e Sarawak; sede non confermata.</t>
         </is>
       </c>
-      <c r="J103" s="3" t="inlineStr">
+      <c r="K109" s="3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J103"/>
+  <autoFilter ref="A1:K109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7890,18 +9390,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7942,10 +9443,15 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -7974,10 +9480,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Detergenti e chimici, non attrezzature: probabilmente fuori target.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8011,10 +9522,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Chimici per pulizia industriale. Fonte debole, probabilmente fuori target.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8043,10 +9559,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Elettroutensili, saldatrici, DPI. Fonte poco affidabile.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8068,6 +9589,11 @@
           <t>Muar</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>http://www.glbosun.com.my/</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -8075,10 +9601,15 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Utensili e ferramenta, fondata 2000.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>Utensili e ferramenta, fondata 2000. | VERIFICA: Lot 1745 Jalan Naib Kadir, Bukit Pasir, Muar. Sito citato nei risultati, non aperto. Nome Bosun = marchio cinese: possibile conflitto su utensili diamantati/elettrici.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8100,6 +9631,11 @@
           <t>Johor Bahru</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>http://www.sumitec.my</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -8107,10 +9643,15 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Utensili di precisione, misura, manutenzione. Fondata 2007.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>Utensili di precisione, misura, manutenzione. Fondata 2007. | VERIFICA: No.35 Jalan Tiong Emas, Tiong Nam, Johor Bahru. Distributore di utensili di precisione/misura da principals. Sito citato, non aperto.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8144,10 +9685,15 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Attrezzature sabbiatura, rivestimenti, DPI. Fondata 1997. Sito proprio non trovato (pagina directory).</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>Attrezzature sabbiatura, rivestimenti, DPI. Fondata 1997. Sito proprio non trovato (pagina directory). | VERIFICA: Sede discordante (Singapore o Johor Bahru); un'unica fonte; sito non trovato.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8176,10 +9722,15 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>Elettroutensili, saldatrici, DPI. Fonte poco affidabile.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8208,10 +9759,15 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Produttore di saldatrici automatiche e fili animati.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8228,18 +9784,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8280,10 +9837,15 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -8312,10 +9874,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Rivenditore dal 1991: utensili, saldatura, aspirapolveri, compressori. Candidato più rilevante in Kedah.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>Rivenditore dal 1991: utensili, saldatura, aspirapolveri, compressori. Candidato più rilevante in Kedah. | VERIFICA: Vende/ripara/noleggia macchinari (pompe, compressori, soffiatori, lavapavimenti, aspirapolvere). Coerente con Cleaning, meno con Utensileria e Welding.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8349,10 +9916,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Il nome indica un produttore.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8366,12 +9938,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H.E. Trading (S.P) Sdn. Bhd.</t>
+          <t>CR Hardware Sdn Bhd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sungai Petani (Jalan Kuala Ketil)</t>
+          <t>250-C Jalan Tunku Putra, Kulim</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://mall.lapasar.com/supplier-profile/cr-hardware</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8381,10 +9958,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rivenditore dal 1991: utensili, saldatura, aspirapolveri, compressori. Candidato più rilevante in Kedah.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>Utensili manuali ed elettrici, fornitore B2B (profilo marketplace). 2° giro.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8393,30 +9975,72 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Utensileria</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H.E. Trading (S.P) Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sungai Petani (Jalan Kuala Ketil)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Candidato</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Parziale</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Rivenditore dal 1991: utensili, saldatura, aspirapolveri, compressori. Candidato più rilevante in Kedah. | VERIFICA: Vende/ripara/noleggia macchinari (pompe, compressori, soffiatori, lavapavimenti, aspirapolvere). Coerente con Cleaning, meno con Utensileria e Welding.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>DA VERIFICARE UMANAMENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Welding</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>H.E. Trading (S.P) Sdn. Bhd.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Sungai Petani (Jalan Kuala Ketil)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Candidato</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Rivenditore dal 1991: utensili, saldatura, aspirapolveri, compressori. Candidato più rilevante in Kedah.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Parziale</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Rivenditore dal 1991: utensili, saldatura, aspirapolveri, compressori. Candidato più rilevante in Kedah. | VERIFICA: Vende/ripara/noleggia macchinari (pompe, compressori, soffiatori, lavapavimenti, aspirapolvere). Coerente con Cleaning, meno con Utensileria e Welding.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8433,18 +10057,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8485,10 +10110,15 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -8517,10 +10147,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Catena ferramenta; presenza in Kelantan non confermata.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8529,22 +10164,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Utensileria</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SLS Kelantan Sdn. Bhd.</t>
+          <t>Hassan Abdullah Hardware Sdn. Bhd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jalan Kuala Krai, Kota Bharu</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>09-744 9555</t>
+          <t>Ketereh (Kota Bharu)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8554,10 +10184,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Attività non confermata.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>Ferramenta generale, fondata 1983. Non chiaro se venda a clienti B2B industriali. 2° giro.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8566,22 +10201,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Meccanica</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KB Genset</t>
+          <t>SLS Kelantan Sdn. Bhd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jalan Mahmud, Kota Bharu</t>
+          <t>Jalan Kuala Krai, Kota Bharu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>019-379 3191</t>
+          <t>09-744 9555</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8591,10 +10226,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Probabile generatori, attività non confermata.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>Attività non confermata.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8608,30 +10248,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New Ah Piar Motor</t>
+          <t>Hassan Abdullah Hardware Sdn. Bhd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kampung Wakar Che Yeh, Kota Bharu</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>09-748 1497</t>
+          <t>Ketereh (Kota Bharu)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Probabile cliente finale</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Probabile officina/motori.</t>
+          <t>Non ancora verificata</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>Ferramenta generale, fondata 1983. Non chiaro se venda a clienti B2B industriali. 2° giro.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8645,30 +10285,119 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>KB Genset</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Jalan Mahmud, Kota Bharu</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>019-379 3191</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Debole / da verificare</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Probabile generatori, attività non confermata.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>DA VERIFICARE UMANAMENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Meccanica</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>New Ah Piar Motor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Kampung Wakar Che Yeh, Kota Bharu</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>09-748 1497</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Probabile cliente finale</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Probabile officina/motori.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>DA VERIFICARE UMANAMENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Meccanica</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>SLS Kelantan Sdn. Bhd.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Jalan Kuala Krai, Kota Bharu</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>09-744 9555</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Debole / da verificare</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Attività non confermata.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8685,18 +10414,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8737,10 +10467,15 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -8774,10 +10509,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Produttore di detergenti chimici.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8801,15 +10541,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Debole / da verificare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Strumenti di misura e collaudo di precisione.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>Strumenti di misura e collaudo di precisione. | VERIFICA: 30 Jalan IMJ 1, Taman Industri Malim Jaya, Melaka. Distributore esclusivo PRECISE e VIEW MASTER: strumenti di misura, non utensileria in senso stretto.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8838,10 +10583,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Macchinari, hardware e utensili industriali dal 1993.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>Macchinari, hardware e utensili industriali dal 1993. | VERIFICA: 146-B/C Jalan Kesidang 1/10, Bachang, Melaka. SSM 200501015289. Rivenditore generalista. Sito non trovato.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8870,10 +10620,15 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Dal 1980; probabile negozio al dettaglio.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8902,10 +10657,15 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Produttore di prodotti per saldatura (gruppo Leeden NOX).</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8934,10 +10694,15 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Macchinari, hardware e utensili industriali dal 1993.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>Macchinari, hardware e utensili industriali dal 1993. | VERIFICA: 146-B/C Jalan Kesidang 1/10, Bachang, Melaka. SSM 200501015289. Rivenditore generalista. Sito non trovato.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -8954,18 +10719,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9006,10 +10772,15 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -9038,10 +10809,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Impresa di servizi di pulizia: probabile cliente finale.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -9058,18 +10834,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9110,10 +10887,15 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -9147,10 +10929,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fornitore B2B wholesale (power tools, elettrico). Unico candidato locale in Pahang.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>Fornitore B2B wholesale (power tools, elettrico). Unico candidato locale in Pahang. | VERIFICA: SSM 201303295436. Sito proprio non trovato. Il nome richiama il marchio tedesco KS Tools: verificare conflitto.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -9167,18 +10954,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9219,10 +11007,15 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>esito_verifica</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>stato_verifica</t>
         </is>
@@ -9251,10 +11044,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Attrezzature/utensili/adesivi industriali; da verificare se rivenditore.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -9283,10 +11081,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Utensili da taglio in metallo duro, ceramica, CBN, PCD.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>Utensili da taglio in metallo duro, ceramica, CBN, PCD. | VERIFICA: 24-26 Lorong Nagasari 9, Taman Nagasari, Perai. Utensili da taglio. Dominio alloytool.com.my solo da riassunto di ricerca, da confermare. Marchi non verificati.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -9315,10 +11118,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hardware industriale, macchinari, utensili. Dal 1983.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>Hardware industriale, macchinari, utensili. Dal 1983. | VERIFICA: Jalan Heng Choon Thian, Butterworth. Pagina Invest Penang non leggibile. Welding non confermato.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -9340,6 +11148,11 @@
           <t>Perai</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>http://dynarco.com/</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -9347,10 +11160,15 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Macchinari per precision tooling.</t>
+          <t>Confermato (riserva sul settore)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>Macchinari per precision tooling. | VERIFICA: 9 Jalan Todak 5, Seberang Jaya, Perai (+ Puchong). Piu macchine utensili (rettificatrici, EDM, CNC) che utensileria di consumo. Sito da riassunto di ricerca, non aperto.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -9372,17 +11190,37 @@
           <t>Penang</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>www.edmtools.com.my</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+603-8062 5918 / +603-8060 3117 (numeri della sede Selangor)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>info@edmtools.com.my</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Candidato</t>
+          <t>Produttore / possibile concorrente</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Materiali e accessori EDM, dal 1988.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>Materiali e accessori EDM, dal 1988. | VERIFICA: Sede a Prai (26 Lorong Nagasari 3). Produttore fili EDM in ottone e distributore esclusivo Erowa, Elbo Controlli, Thome, Toltec, Hwacheon; controllata di societa quotata.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -9411,10 +11249,15 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>Non ancora verificata</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Dust collector, fumi di saldatura: produttore/installatore.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -9443,10 +11286,15 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hardware industriale, macchinari, utensili. Dal 1983.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>Hardware industriale, macchinari, utensili. Dal 1983. | VERIFICA: Jalan Heng Choon Thian, Butterworth. Pagina Invest Penang non leggibile. Welding non confermato.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -9475,10 +11323,15 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Gas industriali e attrezzature di saldatura. Dichiara di servire anche Kedah.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
+        <is>
+          <t>Gas industriali e attrezzature di saldatura. Dichiara di servire anche Kedah. | VERIFICA: Dal 1984, Mak Mandin, Butterworth. Gas industriali + attrezzature e consumabili di saldatura. Pagina fonte non leggibile.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -9507,10 +11360,15 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hardware industriale, macchinari, utensili. Dal 1983.</t>
+          <t>Parziale</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
+        <is>
+          <t>Hardware industriale, macchinari, utensili. Dal 1983. | VERIFICA: Jalan Heng Choon Thian, Butterworth. Pagina Invest Penang non leggibile. Welding non confermato.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -9532,6 +11390,16 @@
           <t>Jalan Chain Ferry, Perai</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://ecpneumatic.com.my/</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+604 380 1277 / 78; +6012 528 2779 (WhatsApp)</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Candidato</t>
@@ -9539,10 +11407,15 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Componenti pneumatici e hardware.</t>
+          <t>Confermato (settore pneumatica)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
+        <is>
+          <t>Componenti pneumatici e hardware. | VERIFICA: Email offuscata sul sito. Distributore dal 2006: SMC, Parker, Festo, Norgren, Camozzi, CKD; marchio proprio SWISH. Nessun conflitto diretto con Dupuy rilevato.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
@@ -9571,10 +11444,15 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Distributore/stockist fasteners e ferramenta elettromeccanica.</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>Distributore/stockist fasteners e ferramenta elettromeccanica. | VERIFICA: 15 Jalan Industri Impian 1, Bukit Mertajam (filiale a Johor Bahru). Fondata 1998. Fasteners/ricambi: Meccanica solo in senso lato.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
         </is>
